--- a/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
+++ b/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\SevSU\2_Course\3_Term\Applied_Math_in_AI\lab_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5809F6-CFDA-4E28-9E91-C39E6AE8934F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E640256-294A-4E95-9B56-F26242B70C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10695" yWindow="0" windowWidth="18210" windowHeight="17385" firstSheet="2" activeTab="2" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Инициализация" sheetId="1" r:id="rId1"/>
@@ -945,15 +945,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -962,18 +959,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -986,13 +971,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1026,6 +1004,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2081,7 +2077,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:numRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2089,7 +2085,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:numRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -2375,7 +2371,7 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:filteredCategoryTitle>
                 <c15:cat>
-                  <c:numRef>
+                  <c:multiLvlStrRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
@@ -2383,7 +2379,7 @@
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
-                  </c:numRef>
+                  </c:multiLvlStrRef>
                 </c15:cat>
               </c15:filteredCategoryTitle>
             </c:ext>
@@ -5549,10 +5545,10 @@
         <f t="shared" si="0"/>
         <v>4437</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -5680,20 +5676,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="5">
+      <c r="L1" s="4">
         <f>A18-A2</f>
         <v>16</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="27" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5705,14 +5701,14 @@
         <f>POWER(A2,4)+8*POWER(A2,3)-6*POWER(A2,2)-72*A2+90</f>
         <v>2210</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <f>(A18+A2)/2</f>
         <v>-2</v>
       </c>
-      <c r="S2" s="18"/>
+      <c r="S2" s="27"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -5722,14 +5718,14 @@
         <f t="shared" ref="B3:B18" si="0">POWER(A3,4)+8*POWER(A3,3)-6*POWER(A3,2)-72*A3+90</f>
         <v>981</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <f>POWER(L2,4)+8*POWER(L2,3)-6*POWER(L2,2)-72*L2+90</f>
         <v>162</v>
       </c>
-      <c r="S3" s="18"/>
+      <c r="S3" s="27"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -5739,14 +5735,14 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <f>A2+L1/4</f>
         <v>-6</v>
       </c>
-      <c r="S4" s="18"/>
+      <c r="S4" s="27"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -5756,14 +5752,14 @@
         <f t="shared" si="0"/>
         <v>-43</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <f>A18-L1/4</f>
         <v>2</v>
       </c>
-      <c r="S5" s="18"/>
+      <c r="S5" s="27"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -5773,14 +5769,14 @@
         <f t="shared" si="0"/>
         <v>-126</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="4">
         <f>POWER(L4,4)+8*POWER(L4,3)-6*POWER(L4,2)-72*L4+90</f>
         <v>-126</v>
       </c>
-      <c r="S6" s="18"/>
+      <c r="S6" s="27"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -5790,14 +5786,14 @@
         <f t="shared" si="0"/>
         <v>-75</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="4">
         <f>POWER(L5,4)+8*POWER(L5,3)-6*POWER(L5,2)-72*L5+90</f>
         <v>2</v>
       </c>
-      <c r="S7" s="18"/>
+      <c r="S7" s="27"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -5807,7 +5803,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="S8" s="18"/>
+      <c r="S8" s="27"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
@@ -5817,17 +5813,16 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="18"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="26"/>
+      <c r="S9" s="27"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -5837,7 +5832,7 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="S10" s="18"/>
+      <c r="S10" s="27"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
@@ -5847,14 +5842,14 @@
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="4">
         <f>L2-A2</f>
         <v>8</v>
       </c>
-      <c r="S11" s="18"/>
+      <c r="S11" s="27"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
@@ -5864,17 +5859,16 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="18"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="26"/>
+      <c r="S12" s="27"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -5884,7 +5878,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="S13" s="18"/>
+      <c r="S13" s="27"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -5894,7 +5888,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S14" s="18"/>
+      <c r="S14" s="27"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -5904,7 +5898,7 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="S15" s="18"/>
+      <c r="S15" s="27"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -5914,7 +5908,7 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="S16" s="18"/>
+      <c r="S16" s="27"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -5924,7 +5918,7 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="S17" s="18"/>
+      <c r="S17" s="27"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -5934,32 +5928,32 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="S18" s="18"/>
+      <c r="S18" s="27"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="S19" s="18"/>
-    </row>
-    <row r="20" spans="1:19" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
+      <c r="S19" s="27"/>
+    </row>
+    <row r="20" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="4">
         <f>A30-A22</f>
         <v>8</v>
       </c>
-      <c r="S21" s="18" t="s">
+      <c r="S21" s="27" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5968,189 +5962,189 @@
         <v>-10</v>
       </c>
       <c r="B22" s="2">
-        <f>POWER(A22,4)+8*POWER(A22,3)-6*POWER(A22,2)-72*A22+90</f>
+        <f t="shared" ref="B22:B30" si="1">POWER(A22,4)+8*POWER(A22,3)-6*POWER(A22,2)-72*A22+90</f>
         <v>2210</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="4">
         <f>(A30+A22)/2</f>
         <v>-6</v>
       </c>
-      <c r="S22" s="18"/>
+      <c r="S22" s="27"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>-9</v>
       </c>
       <c r="B23" s="2">
-        <f>POWER(A23,4)+8*POWER(A23,3)-6*POWER(A23,2)-72*A23+90</f>
+        <f t="shared" si="1"/>
         <v>981</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="4">
         <f>POWER(L22,4)+8*POWER(L22,3)-6*POWER(L22,2)-72*L22+90</f>
         <v>-126</v>
       </c>
-      <c r="S23" s="18"/>
+      <c r="S23" s="27"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>-8</v>
       </c>
       <c r="B24" s="2">
-        <f>POWER(A24,4)+8*POWER(A24,3)-6*POWER(A24,2)-72*A24+90</f>
+        <f t="shared" si="1"/>
         <v>282</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="4">
         <f>A22+L21/4</f>
         <v>-8</v>
       </c>
-      <c r="S24" s="18"/>
+      <c r="S24" s="27"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>-7</v>
       </c>
       <c r="B25" s="2">
-        <f>POWER(A25,4)+8*POWER(A25,3)-6*POWER(A25,2)-72*A25+90</f>
+        <f t="shared" si="1"/>
         <v>-43</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="4">
         <f>A30-L21/4</f>
         <v>-4</v>
       </c>
-      <c r="S25" s="18"/>
+      <c r="S25" s="27"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>-6</v>
       </c>
       <c r="B26" s="2">
-        <f>POWER(A26,4)+8*POWER(A26,3)-6*POWER(A26,2)-72*A26+90</f>
+        <f t="shared" si="1"/>
         <v>-126</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="5">
+      <c r="L26" s="4">
         <f>POWER(L24,4)+8*POWER(L24,3)-6*POWER(L24,2)-72*L24+90</f>
         <v>282</v>
       </c>
-      <c r="S26" s="18"/>
+      <c r="S26" s="27"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>-5</v>
       </c>
       <c r="B27" s="2">
-        <f>POWER(A27,4)+8*POWER(A27,3)-6*POWER(A27,2)-72*A27+90</f>
+        <f t="shared" si="1"/>
         <v>-75</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="4">
         <f>POWER(L25,4)+8*POWER(L25,3)-6*POWER(L25,2)-72*L25+90</f>
         <v>26</v>
       </c>
-      <c r="S27" s="18"/>
+      <c r="S27" s="27"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>-4</v>
       </c>
       <c r="B28" s="2">
-        <f>POWER(A28,4)+8*POWER(A28,3)-6*POWER(A28,2)-72*A28+90</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="S28" s="18"/>
+      <c r="S28" s="27"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>-3</v>
       </c>
       <c r="B29" s="2">
-        <f>POWER(A29,4)+8*POWER(A29,3)-6*POWER(A29,2)-72*A29+90</f>
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="8"/>
-      <c r="S29" s="18"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="26"/>
+      <c r="S29" s="27"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>-2</v>
       </c>
       <c r="B30" s="2">
-        <f>POWER(A30,4)+8*POWER(A30,3)-6*POWER(A30,2)-72*A30+90</f>
+        <f t="shared" si="1"/>
         <v>162</v>
       </c>
-      <c r="S30" s="18"/>
+      <c r="S30" s="27"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L31" s="5">
+      <c r="L31" s="4">
         <f>L25-L24</f>
         <v>4</v>
       </c>
-      <c r="S31" s="18"/>
+      <c r="S31" s="27"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K32" s="9" t="s">
+      <c r="K32" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="11"/>
-      <c r="S32" s="18"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="23"/>
+      <c r="S32" s="27"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S33" s="18"/>
+      <c r="S33" s="27"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S34" s="18"/>
+      <c r="S34" s="27"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S35" s="18"/>
-    </row>
-    <row r="36" spans="1:19" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="S35" s="27"/>
+    </row>
+    <row r="36" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L37" s="5">
+      <c r="L37" s="4">
         <f>A42-A38</f>
         <v>4</v>
       </c>
-      <c r="S37" s="19" t="s">
+      <c r="S37" s="28" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6162,14 +6156,14 @@
         <f>POWER(A38,4)+8*POWER(A38,3)-6*POWER(A38,2)-72*A38+90</f>
         <v>282</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="5">
+      <c r="L38" s="4">
         <f>(A38+A42)/2</f>
         <v>-6</v>
       </c>
-      <c r="S38" s="19"/>
+      <c r="S38" s="28"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -6179,14 +6173,14 @@
         <f>POWER(A39,4)+8*POWER(A39,3)-6*POWER(A39,2)-72*A39+90</f>
         <v>-43</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39" s="4">
         <f>POWER(L38,4)+8*POWER(L38,3)-6*POWER(L38,2)-72*L38+90</f>
         <v>-126</v>
       </c>
-      <c r="S39" s="19"/>
+      <c r="S39" s="28"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -6196,14 +6190,14 @@
         <f>POWER(A40,4)+8*POWER(A40,3)-6*POWER(A40,2)-72*A40+90</f>
         <v>-126</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L40" s="5">
+      <c r="L40" s="4">
         <f>A38+L37/4</f>
         <v>-7</v>
       </c>
-      <c r="S40" s="19"/>
+      <c r="S40" s="28"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -6213,14 +6207,14 @@
         <f>POWER(A41,4)+8*POWER(A41,3)-6*POWER(A41,2)-72*A41+90</f>
         <v>-75</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L41" s="5">
+      <c r="L41" s="4">
         <f>A42-L37/4</f>
         <v>-5</v>
       </c>
-      <c r="S41" s="19"/>
+      <c r="S41" s="28"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -6230,97 +6224,97 @@
         <f>POWER(A42,4)+8*POWER(A42,3)-6*POWER(A42,2)-72*A42+90</f>
         <v>26</v>
       </c>
-      <c r="K42" s="4" t="s">
+      <c r="K42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L42" s="5">
+      <c r="L42" s="4">
         <f>POWER(L40,4)+8*POWER(L40,3)-6*POWER(L40,2)-72*L40+90</f>
         <v>-43</v>
       </c>
-      <c r="S42" s="19"/>
+      <c r="S42" s="28"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="K43" s="4" t="s">
+      <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="5">
+      <c r="L43" s="4">
         <f>POWER(L41,4)+8*POWER(L41,3)-6*POWER(L41,2)-72*L41+90</f>
         <v>-75</v>
       </c>
-      <c r="S43" s="19"/>
+      <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="S44" s="19"/>
+      <c r="S44" s="28"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="8"/>
-      <c r="S45" s="19"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="25"/>
+      <c r="P45" s="25"/>
+      <c r="Q45" s="26"/>
+      <c r="S45" s="28"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="S46" s="19"/>
+      <c r="S46" s="28"/>
     </row>
     <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
-      <c r="K47" s="4" t="s">
+      <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="5">
+      <c r="L47" s="4">
         <f>L41-L40</f>
         <v>2</v>
       </c>
-      <c r="S47" s="19"/>
+      <c r="S47" s="28"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="K48" s="9" t="s">
+      <c r="K48" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="11"/>
-      <c r="S48" s="19"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="23"/>
+      <c r="S48" s="28"/>
     </row>
     <row r="49" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S49" s="19"/>
+      <c r="S49" s="28"/>
     </row>
     <row r="50" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S50" s="19"/>
+      <c r="S50" s="28"/>
     </row>
     <row r="51" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S51" s="19"/>
+      <c r="S51" s="28"/>
     </row>
     <row r="52" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S52" s="19"/>
+      <c r="S52" s="28"/>
     </row>
     <row r="53" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S53" s="19"/>
+      <c r="S53" s="28"/>
     </row>
     <row r="54" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S54" s="19"/>
+      <c r="S54" s="28"/>
     </row>
     <row r="55" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S55" s="19"/>
+      <c r="S55" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -6345,20 +6339,20 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="20"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="22">
+      <c r="E1" s="12">
         <f>A2</f>
         <v>-10</v>
       </c>
@@ -6371,10 +6365,10 @@
         <f>POWER(A2,4)+8*POWER(A2,3)-6*POWER(A2,2)-72*A2+90</f>
         <v>2210</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="12">
         <f>A18</f>
         <v>6</v>
       </c>
@@ -6387,10 +6381,10 @@
         <f t="shared" ref="B3:B18" si="0">POWER(A3,4)+8*POWER(A3,3)-6*POWER(A3,2)-72*A3+90</f>
         <v>981</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="12">
         <f>E2-E1</f>
         <v>16</v>
       </c>
@@ -6403,10 +6397,10 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="12">
         <f>E3/0.05</f>
         <v>320</v>
       </c>
@@ -6433,10 +6427,10 @@
         <f t="shared" si="0"/>
         <v>-43</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="14">
         <v>14</v>
       </c>
     </row>
@@ -6448,10 +6442,10 @@
         <f t="shared" si="0"/>
         <v>-126</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="14">
         <f>E1+(Числа_Фибоначчи!A15/Числа_Фибоначчи!A17)*E3</f>
         <v>-3.8885410144020041</v>
       </c>
@@ -6464,10 +6458,10 @@
         <f t="shared" si="0"/>
         <v>-75</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="14">
         <f>E1+(Числа_Фибоначчи!A16/Числа_Фибоначчи!A17)*E3</f>
         <v>-0.11145898559799683</v>
       </c>
@@ -6480,10 +6474,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="14">
         <f>POWER(E6,4)+8*POWER(E6,3)-6*POWER(E6,2)-72*E6+90</f>
         <v>37.506272869048132</v>
       </c>
@@ -6496,10 +6490,10 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="14">
         <f>POWER(E7,4)+8*POWER(E7,3)-6*POWER(E7,2)-72*E7+90</f>
         <v>97.939585329912319</v>
       </c>
@@ -6512,10 +6506,10 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="14">
         <f>E7</f>
         <v>-0.11145898559799683</v>
       </c>
@@ -6528,10 +6522,10 @@
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="14">
         <f>E6</f>
         <v>-3.8885410144020041</v>
       </c>
@@ -6544,10 +6538,10 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="16">
         <f>E5-1</f>
         <v>13</v>
       </c>
@@ -6560,10 +6554,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="16">
         <f>E1+(Числа_Фибоначчи!A14/Числа_Фибоначчи!A16)*(E10-E1)</f>
         <v>-6.2229179711959928</v>
       </c>
@@ -6576,10 +6570,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="16">
         <f>POWER(E13,4)+8*POWER(E13,3)-6*POWER(E13,2)-72*E13+90</f>
         <v>-122.54059347706982</v>
       </c>
@@ -6592,10 +6586,10 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="16">
         <f>E11</f>
         <v>-3.8885410144020041</v>
       </c>
@@ -6608,10 +6602,10 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="16">
         <f>E13</f>
         <v>-6.2229179711959928</v>
       </c>
@@ -6624,10 +6618,10 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="18">
         <f>E12-1</f>
         <v>12</v>
       </c>
@@ -6640,91 +6634,91 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="18">
         <f>E1+(Числа_Фибоначчи!A13/Числа_Фибоначчи!A15)*(E15-E1)</f>
         <v>-7.6656230432060113</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="18">
         <f>POWER(E18,4)+8*POWER(E18,3)-6*POWER(E18,2)-72*E18+90</f>
         <v>138.73556061626778</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="18">
         <f>E18</f>
         <v>-7.6656230432060113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="18">
         <f>E16</f>
         <v>-6.2229179711959928</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="20">
         <f>E17-1</f>
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="20">
         <f>E20+(Числа_Фибоначчи!A12/Числа_Фибоначчи!A13)*(E15-E20)</f>
         <v>-5.33128908549023</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="20">
         <f>POWER(E23,4)+8*POWER(E23,3)-6*POWER(E23,2)-72*E23+90</f>
         <v>-101.07101742715895</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="20">
         <f>E21</f>
         <v>-6.2229179711959928</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="20">
         <f>E23</f>
         <v>-5.33128908549023</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="10">
         <f>E22-1</f>
         <v>10</v>
       </c>

--- a/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
+++ b/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\SevSU\2_Course\3_Term\Applied_Math_in_AI\lab_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E640256-294A-4E95-9B56-F26242B70C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F573EB-CE40-4ADC-ABBC-7045E042EE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="1" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="2" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Инициализация" sheetId="1" r:id="rId1"/>
     <sheet name="Итерации 1-3 Деление интервала" sheetId="2" r:id="rId2"/>
-    <sheet name="Итерации 1-3 Фибоначчи" sheetId="5" r:id="rId3"/>
+    <sheet name="Итерации 1-4 Фибоначчи" sheetId="5" r:id="rId3"/>
     <sheet name="Числа_Фибоначчи" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="237">
   <si>
     <t>f(x)</t>
   </si>
@@ -787,13 +787,13 @@
     <t>F_209</t>
   </si>
   <si>
-    <t>F_0</t>
-  </si>
-  <si>
-    <t>F_12 =</t>
-  </si>
-  <si>
     <t xml:space="preserve">f(x_1) = </t>
+  </si>
+  <si>
+    <t>F_210</t>
+  </si>
+  <si>
+    <t>F_14 =</t>
   </si>
 </sst>
 </file>
@@ -945,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,9 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -5689,7 +5686,7 @@
         <f>A18-A2</f>
         <v>16</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="26" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5708,7 +5705,7 @@
         <f>(A18+A2)/2</f>
         <v>-2</v>
       </c>
-      <c r="S2" s="27"/>
+      <c r="S2" s="26"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -5725,7 +5722,7 @@
         <f>POWER(L2,4)+8*POWER(L2,3)-6*POWER(L2,2)-72*L2+90</f>
         <v>162</v>
       </c>
-      <c r="S3" s="27"/>
+      <c r="S3" s="26"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -5742,7 +5739,7 @@
         <f>A2+L1/4</f>
         <v>-6</v>
       </c>
-      <c r="S4" s="27"/>
+      <c r="S4" s="26"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -5759,7 +5756,7 @@
         <f>A18-L1/4</f>
         <v>2</v>
       </c>
-      <c r="S5" s="27"/>
+      <c r="S5" s="26"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -5776,7 +5773,7 @@
         <f>POWER(L4,4)+8*POWER(L4,3)-6*POWER(L4,2)-72*L4+90</f>
         <v>-126</v>
       </c>
-      <c r="S6" s="27"/>
+      <c r="S6" s="26"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -5793,7 +5790,7 @@
         <f>POWER(L5,4)+8*POWER(L5,3)-6*POWER(L5,2)-72*L5+90</f>
         <v>2</v>
       </c>
-      <c r="S7" s="27"/>
+      <c r="S7" s="26"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -5803,7 +5800,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="S8" s="27"/>
+      <c r="S8" s="26"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
@@ -5813,16 +5810,16 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="26"/>
-      <c r="S9" s="27"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="25"/>
+      <c r="S9" s="26"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -5832,7 +5829,7 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="S10" s="27"/>
+      <c r="S10" s="26"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
@@ -5849,7 +5846,7 @@
         <f>L2-A2</f>
         <v>8</v>
       </c>
-      <c r="S11" s="27"/>
+      <c r="S11" s="26"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
@@ -5859,16 +5856,16 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="26"/>
-      <c r="S12" s="27"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="25"/>
+      <c r="S12" s="26"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -5878,7 +5875,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="S13" s="27"/>
+      <c r="S13" s="26"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -5888,7 +5885,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="26"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -5898,7 +5895,7 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="S15" s="27"/>
+      <c r="S15" s="26"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -5908,7 +5905,7 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="S16" s="27"/>
+      <c r="S16" s="26"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -5918,7 +5915,7 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="S17" s="27"/>
+      <c r="S17" s="26"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -5928,16 +5925,16 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="S18" s="27"/>
+      <c r="S18" s="26"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="S19" s="27"/>
-    </row>
-    <row r="20" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="S19" s="26"/>
+    </row>
+    <row r="20" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -5953,7 +5950,7 @@
         <f>A30-A22</f>
         <v>8</v>
       </c>
-      <c r="S21" s="27" t="s">
+      <c r="S21" s="26" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5972,7 +5969,7 @@
         <f>(A30+A22)/2</f>
         <v>-6</v>
       </c>
-      <c r="S22" s="27"/>
+      <c r="S22" s="26"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -5989,7 +5986,7 @@
         <f>POWER(L22,4)+8*POWER(L22,3)-6*POWER(L22,2)-72*L22+90</f>
         <v>-126</v>
       </c>
-      <c r="S23" s="27"/>
+      <c r="S23" s="26"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -6006,7 +6003,7 @@
         <f>A22+L21/4</f>
         <v>-8</v>
       </c>
-      <c r="S24" s="27"/>
+      <c r="S24" s="26"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -6023,7 +6020,7 @@
         <f>A30-L21/4</f>
         <v>-4</v>
       </c>
-      <c r="S25" s="27"/>
+      <c r="S25" s="26"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -6040,7 +6037,7 @@
         <f>POWER(L24,4)+8*POWER(L24,3)-6*POWER(L24,2)-72*L24+90</f>
         <v>282</v>
       </c>
-      <c r="S26" s="27"/>
+      <c r="S26" s="26"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -6057,7 +6054,7 @@
         <f>POWER(L25,4)+8*POWER(L25,3)-6*POWER(L25,2)-72*L25+90</f>
         <v>26</v>
       </c>
-      <c r="S27" s="27"/>
+      <c r="S27" s="26"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
@@ -6067,7 +6064,7 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="S28" s="27"/>
+      <c r="S28" s="26"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
@@ -6077,16 +6074,16 @@
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="K29" s="24" t="s">
+      <c r="K29" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="26"/>
-      <c r="S29" s="27"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="25"/>
+      <c r="S29" s="26"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -6096,7 +6093,7 @@
         <f t="shared" si="1"/>
         <v>162</v>
       </c>
-      <c r="S30" s="27"/>
+      <c r="S30" s="26"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K31" s="3" t="s">
@@ -6106,30 +6103,30 @@
         <f>L25-L24</f>
         <v>4</v>
       </c>
-      <c r="S31" s="27"/>
+      <c r="S31" s="26"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K32" s="21" t="s">
+      <c r="K32" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="23"/>
-      <c r="S32" s="27"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="22"/>
+      <c r="S32" s="26"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S33" s="27"/>
+      <c r="S33" s="26"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S34" s="27"/>
+      <c r="S34" s="26"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S35" s="27"/>
-    </row>
-    <row r="36" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="S35" s="26"/>
+    </row>
+    <row r="36" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>1</v>
@@ -6144,7 +6141,7 @@
         <f>A42-A38</f>
         <v>4</v>
       </c>
-      <c r="S37" s="28" t="s">
+      <c r="S37" s="27" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6163,7 +6160,7 @@
         <f>(A38+A42)/2</f>
         <v>-6</v>
       </c>
-      <c r="S38" s="28"/>
+      <c r="S38" s="27"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -6180,7 +6177,7 @@
         <f>POWER(L38,4)+8*POWER(L38,3)-6*POWER(L38,2)-72*L38+90</f>
         <v>-126</v>
       </c>
-      <c r="S39" s="28"/>
+      <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -6197,7 +6194,7 @@
         <f>A38+L37/4</f>
         <v>-7</v>
       </c>
-      <c r="S40" s="28"/>
+      <c r="S40" s="27"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -6214,7 +6211,7 @@
         <f>A42-L37/4</f>
         <v>-5</v>
       </c>
-      <c r="S41" s="28"/>
+      <c r="S41" s="27"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -6231,7 +6228,7 @@
         <f>POWER(L40,4)+8*POWER(L40,3)-6*POWER(L40,2)-72*L40+90</f>
         <v>-43</v>
       </c>
-      <c r="S42" s="28"/>
+      <c r="S42" s="27"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
@@ -6243,31 +6240,31 @@
         <f>POWER(L41,4)+8*POWER(L41,3)-6*POWER(L41,2)-72*L41+90</f>
         <v>-75</v>
       </c>
-      <c r="S43" s="28"/>
+      <c r="S43" s="27"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="S44" s="28"/>
+      <c r="S44" s="27"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="K45" s="24" t="s">
+      <c r="K45" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="25"/>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="26"/>
-      <c r="S45" s="28"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="25"/>
+      <c r="S45" s="27"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="S46" s="28"/>
+      <c r="S46" s="27"/>
     </row>
     <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
@@ -6279,42 +6276,42 @@
         <f>L41-L40</f>
         <v>2</v>
       </c>
-      <c r="S47" s="28"/>
+      <c r="S47" s="27"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="K48" s="21" t="s">
+      <c r="K48" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="22"/>
-      <c r="M48" s="22"/>
-      <c r="N48" s="22"/>
-      <c r="O48" s="22"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="23"/>
-      <c r="S48" s="28"/>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="21"/>
+      <c r="P48" s="21"/>
+      <c r="Q48" s="22"/>
+      <c r="S48" s="27"/>
     </row>
     <row r="49" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S49" s="28"/>
+      <c r="S49" s="27"/>
     </row>
     <row r="50" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S50" s="28"/>
+      <c r="S50" s="27"/>
     </row>
     <row r="51" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S51" s="28"/>
+      <c r="S51" s="27"/>
     </row>
     <row r="52" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S52" s="28"/>
+      <c r="S52" s="27"/>
     </row>
     <row r="53" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S53" s="28"/>
+      <c r="S53" s="27"/>
     </row>
     <row r="54" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S54" s="28"/>
+      <c r="S54" s="27"/>
     </row>
     <row r="55" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S55" s="28"/>
+      <c r="S55" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -6335,29 +6332,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81ADA57-1C13-42F7-B065-32BF7F0FC547}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="5" max="5" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="12">
+      <c r="E1" s="11">
         <f>A2</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>-10</v>
       </c>
@@ -6365,15 +6362,15 @@
         <f>POWER(A2,4)+8*POWER(A2,3)-6*POWER(A2,2)-72*A2+90</f>
         <v>2210</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <f>A18</f>
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>-9</v>
       </c>
@@ -6381,15 +6378,22 @@
         <f t="shared" ref="B3:B18" si="0">POWER(A3,4)+8*POWER(A3,3)-6*POWER(A3,2)-72*A3+90</f>
         <v>981</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <f>E2-E1</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
+        <f>Числа_Фибоначчи!A13</f>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>-8</v>
       </c>
@@ -6397,29 +6401,22 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <f>E3/0.05</f>
         <v>320</v>
       </c>
       <c r="G4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H4">
-        <f>Числа_Фибоначчи!A13</f>
-        <v>233</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4">
         <f>Числа_Фибоначчи!A14</f>
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>-7</v>
       </c>
@@ -6427,14 +6424,14 @@
         <f t="shared" si="0"/>
         <v>-43</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>-6</v>
       </c>
@@ -6442,15 +6439,15 @@
         <f t="shared" si="0"/>
         <v>-126</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>E1+(Числа_Фибоначчи!A15/Числа_Фибоначчи!A17)*E3</f>
         <v>-3.8885410144020041</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>-5</v>
       </c>
@@ -6458,15 +6455,15 @@
         <f t="shared" si="0"/>
         <v>-75</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <f>E1+(Числа_Фибоначчи!A16/Числа_Фибоначчи!A17)*E3</f>
         <v>-0.11145898559799683</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>-4</v>
       </c>
@@ -6474,15 +6471,15 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <f>POWER(E6,4)+8*POWER(E6,3)-6*POWER(E6,2)-72*E6+90</f>
         <v>37.506272869048132</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>-3</v>
       </c>
@@ -6490,15 +6487,15 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <f>POWER(E7,4)+8*POWER(E7,3)-6*POWER(E7,2)-72*E7+90</f>
         <v>97.939585329912319</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>-2</v>
       </c>
@@ -6506,15 +6503,15 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <f>E7</f>
         <v>-0.11145898559799683</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>-1</v>
       </c>
@@ -6522,15 +6519,15 @@
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <f>E6</f>
         <v>-3.8885410144020041</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -6538,15 +6535,15 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="15">
         <f>E5-1</f>
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1</v>
       </c>
@@ -6554,15 +6551,15 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <f>E1+(Числа_Фибоначчи!A14/Числа_Фибоначчи!A16)*(E10-E1)</f>
         <v>-6.2229179711959928</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -6570,15 +6567,15 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <f>POWER(E13,4)+8*POWER(E13,3)-6*POWER(E13,2)-72*E13+90</f>
         <v>-122.54059347706982</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>3</v>
       </c>
@@ -6586,15 +6583,15 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="15">
         <f>E11</f>
         <v>-3.8885410144020041</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -6602,10 +6599,10 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="15">
         <f>E13</f>
         <v>-6.2229179711959928</v>
       </c>
@@ -6618,10 +6615,10 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <f>E12-1</f>
         <v>12</v>
       </c>
@@ -6634,93 +6631,84 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <f>E1+(Числа_Фибоначчи!A13/Числа_Фибоначчи!A15)*(E15-E1)</f>
         <v>-7.6656230432060113</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="E19" s="18">
+      <c r="D19" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="E19" s="17">
         <f>POWER(E18,4)+8*POWER(E18,3)-6*POWER(E18,2)-72*E18+90</f>
         <v>138.73556061626778</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <f>E18</f>
         <v>-7.6656230432060113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <f>E16</f>
         <v>-6.2229179711959928</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="19">
         <f>E17-1</f>
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <f>E20+(Числа_Фибоначчи!A12/Числа_Фибоначчи!A13)*(E15-E20)</f>
         <v>-5.33128908549023</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="19">
         <f>POWER(E23,4)+8*POWER(E23,3)-6*POWER(E23,2)-72*E23+90</f>
         <v>-101.07101742715895</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="19">
         <f>E21</f>
         <v>-6.2229179711959928</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="19">
         <f>E23</f>
         <v>-5.33128908549023</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="10">
-        <f>E22-1</f>
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6742,7 +6730,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6750,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6759,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6768,7 +6756,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6777,7 +6765,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6786,7 +6774,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6795,7 +6783,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -6804,7 +6792,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6813,7 +6801,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6822,7 +6810,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6831,7 +6819,7 @@
         <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -6840,7 +6828,7 @@
         <v>144</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6849,16 +6837,16 @@
         <v>233</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <f t="shared" si="0"/>
+        <f>A12+A13</f>
         <v>377</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6867,7 +6855,7 @@
         <v>610</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -6876,7 +6864,7 @@
         <v>987</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6885,7 +6873,7 @@
         <v>1597</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6894,7 +6882,7 @@
         <v>2584</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6903,7 +6891,7 @@
         <v>4181</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6912,7 +6900,7 @@
         <v>6765</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6921,7 +6909,7 @@
         <v>10946</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6930,7 +6918,7 @@
         <v>17711</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6939,7 +6927,7 @@
         <v>28657</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6948,7 +6936,7 @@
         <v>46368</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6957,7 +6945,7 @@
         <v>75025</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6966,7 +6954,7 @@
         <v>121393</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6975,7 +6963,7 @@
         <v>196418</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6984,7 +6972,7 @@
         <v>317811</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -6993,7 +6981,7 @@
         <v>514229</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -7002,7 +6990,7 @@
         <v>832040</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -7011,7 +6999,7 @@
         <v>1346269</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7020,7 +7008,7 @@
         <v>2178309</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7029,7 +7017,7 @@
         <v>3524578</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7038,7 +7026,7 @@
         <v>5702887</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7047,7 +7035,7 @@
         <v>9227465</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7056,7 +7044,7 @@
         <v>14930352</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7065,7 +7053,7 @@
         <v>24157817</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7074,7 +7062,7 @@
         <v>39088169</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7083,7 +7071,7 @@
         <v>63245986</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7092,7 +7080,7 @@
         <v>102334155</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7101,7 +7089,7 @@
         <v>165580141</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7110,7 +7098,7 @@
         <v>267914296</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7119,7 +7107,7 @@
         <v>433494437</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7128,7 +7116,7 @@
         <v>701408733</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7137,7 +7125,7 @@
         <v>1134903170</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7146,7 +7134,7 @@
         <v>1836311903</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7155,7 +7143,7 @@
         <v>2971215073</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7164,7 +7152,7 @@
         <v>4807526976</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7173,7 +7161,7 @@
         <v>7778742049</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7182,7 +7170,7 @@
         <v>12586269025</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7191,7 +7179,7 @@
         <v>20365011074</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7200,7 +7188,7 @@
         <v>32951280099</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7209,7 +7197,7 @@
         <v>53316291173</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7218,7 +7206,7 @@
         <v>86267571272</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7227,7 +7215,7 @@
         <v>139583862445</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7236,7 +7224,7 @@
         <v>225851433717</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7245,7 +7233,7 @@
         <v>365435296162</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7254,7 +7242,7 @@
         <v>591286729879</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7263,7 +7251,7 @@
         <v>956722026041</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7272,7 +7260,7 @@
         <v>1548008755920</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7281,7 +7269,7 @@
         <v>2504730781961</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7290,7 +7278,7 @@
         <v>4052739537881</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7299,7 +7287,7 @@
         <v>6557470319842</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7308,7 +7296,7 @@
         <v>10610209857723</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7317,7 +7305,7 @@
         <v>17167680177565</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7326,7 +7314,7 @@
         <v>27777890035288</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7335,7 +7323,7 @@
         <v>44945570212853</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7344,7 +7332,7 @@
         <v>72723460248141</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7353,7 +7341,7 @@
         <v>117669030460994</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7362,7 +7350,7 @@
         <v>190392490709135</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7371,7 +7359,7 @@
         <v>308061521170129</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7380,7 +7368,7 @@
         <v>498454011879264</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7389,7 +7377,7 @@
         <v>806515533049393</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7398,7 +7386,7 @@
         <v>1304969544928657</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7407,7 +7395,7 @@
         <v>2111485077978050</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7416,7 +7404,7 @@
         <v>3416454622906707</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7425,7 +7413,7 @@
         <v>5527939700884757</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7434,7 +7422,7 @@
         <v>8944394323791464</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7443,7 +7431,7 @@
         <v>1.447233402467622E+16</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7452,7 +7440,7 @@
         <v>2.3416728348467684E+16</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7461,7 +7449,7 @@
         <v>3.7889062373143904E+16</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7458,7 @@
         <v>6.1305790721611584E+16</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7479,7 +7467,7 @@
         <v>9.9194853094755488E+16</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7488,7 +7476,7 @@
         <v>1.6050064381636707E+17</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -7497,7 +7485,7 @@
         <v>2.5969549691112256E+17</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -7506,7 +7494,7 @@
         <v>4.2019614072748966E+17</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -7515,7 +7503,7 @@
         <v>6.7989163763861222E+17</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -7524,7 +7512,7 @@
         <v>1.1000877783661019E+18</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -7533,7 +7521,7 @@
         <v>1.779979416004714E+18</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -7542,7 +7530,7 @@
         <v>2.880067194370816E+18</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -7551,7 +7539,7 @@
         <v>4.6600466103755305E+18</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -7560,7 +7548,7 @@
         <v>7.5401138047463465E+18</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -7569,7 +7557,7 @@
         <v>1.2200160415121877E+19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7566,7 @@
         <v>1.9740274219868226E+19</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -7587,7 +7575,7 @@
         <v>3.19404346349901E+19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -7596,7 +7584,7 @@
         <v>5.1680708854858326E+19</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -7605,7 +7593,7 @@
         <v>8.3621143489848426E+19</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -7614,7 +7602,7 @@
         <v>1.3530185234470676E+20</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -7623,7 +7611,7 @@
         <v>2.189229958345552E+20</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7632,7 +7620,7 @@
         <v>3.54224848179262E+20</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -7641,7 +7629,7 @@
         <v>5.731478440138172E+20</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -7650,7 +7638,7 @@
         <v>9.273726921930792E+20</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -7659,7 +7647,7 @@
         <v>1.5005205362068963E+21</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -7668,7 +7656,7 @@
         <v>2.4278932283999755E+21</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -7677,7 +7665,7 @@
         <v>3.9284137646068717E+21</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -7686,7 +7674,7 @@
         <v>6.3563069930068477E+21</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -7695,7 +7683,7 @@
         <v>1.028472075761372E+22</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -7704,7 +7692,7 @@
         <v>1.6641027750620568E+22</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -7713,7 +7701,7 @@
         <v>2.6925748508234288E+22</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -7722,7 +7710,7 @@
         <v>4.3566776258854857E+22</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -7731,7 +7719,7 @@
         <v>7.0492524767089141E+22</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -7740,7 +7728,7 @@
         <v>1.1405930102594401E+23</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -7749,7 +7737,7 @@
         <v>1.8455182579303315E+23</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -7758,7 +7746,7 @@
         <v>2.9861112681897715E+23</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -7767,7 +7755,7 @@
         <v>4.831629526120103E+23</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -7776,7 +7764,7 @@
         <v>7.8177407943098749E+23</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -7785,7 +7773,7 @@
         <v>1.2649370320429978E+24</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -7794,7 +7782,7 @@
         <v>2.0467111114739851E+24</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -7803,7 +7791,7 @@
         <v>3.3116481435169827E+24</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -7812,7 +7800,7 @@
         <v>5.3583592549909684E+24</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -7821,7 +7809,7 @@
         <v>8.670007398507951E+24</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -7830,7 +7818,7 @@
         <v>1.4028366653498919E+25</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -7839,7 +7827,7 @@
         <v>2.2698374052006868E+25</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -7848,7 +7836,7 @@
         <v>3.6726740705505786E+25</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -7857,7 +7845,7 @@
         <v>5.9425114757512654E+25</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -7866,7 +7854,7 @@
         <v>9.6151855463018439E+25</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -7875,7 +7863,7 @@
         <v>1.5557697022053108E+26</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -7884,7 +7872,7 @@
         <v>2.5172882568354952E+26</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -7893,7 +7881,7 @@
         <v>4.0730579590408064E+26</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -7902,7 +7890,7 @@
         <v>6.590346215876301E+26</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -7911,7 +7899,7 @@
         <v>1.0663404174917107E+27</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -7920,7 +7908,7 @@
         <v>1.7253750390793408E+27</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -7929,7 +7917,7 @@
         <v>2.7917154565710519E+27</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -7938,7 +7926,7 @@
         <v>4.5170904956503927E+27</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -7947,7 +7935,7 @@
         <v>7.3088059522214451E+27</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -7956,7 +7944,7 @@
         <v>1.1825896447871837E+28</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -7965,7 +7953,7 @@
         <v>1.9134702400093282E+28</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -7974,7 +7962,7 @@
         <v>3.0960598847965122E+28</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -7983,7 +7971,7 @@
         <v>5.0095301248058406E+28</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -7992,7 +7980,7 @@
         <v>8.1055900096023528E+28</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -8001,7 +7989,7 @@
         <v>1.3115120134408193E+29</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -8010,7 +7998,7 @@
         <v>2.1220710144010545E+29</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -8019,7 +8007,7 @@
         <v>3.4335830278418734E+29</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -8028,7 +8016,7 @@
         <v>5.5556540422429276E+29</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>168</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -8037,7 +8025,7 @@
         <v>8.9892370700848011E+29</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -8046,7 +8034,7 @@
         <v>1.454489111232773E+30</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -8055,7 +8043,7 @@
         <v>2.3534128182412531E+30</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -8064,7 +8052,7 @@
         <v>3.8079019294740258E+30</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -8073,7 +8061,7 @@
         <v>6.1613147477152787E+30</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -8082,7 +8070,7 @@
         <v>9.9692166771893045E+30</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -8091,7 +8079,7 @@
         <v>1.6130531424904583E+31</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -8100,7 +8088,7 @@
         <v>2.6099748102093888E+31</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -8109,7 +8097,7 @@
         <v>4.2230279526998473E+31</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -8118,7 +8106,7 @@
         <v>6.8330027629092365E+31</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -8127,7 +8115,7 @@
         <v>1.1056030715609085E+32</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -8136,7 +8124,7 @@
         <v>1.7889033478518321E+32</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -8145,7 +8133,7 @@
         <v>2.8945064194127406E+32</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -8154,7 +8142,7 @@
         <v>4.6834097672645727E+32</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -8163,7 +8151,7 @@
         <v>7.5779161866773133E+32</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -8172,7 +8160,7 @@
         <v>1.2261325953941887E+33</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -8181,7 +8169,7 @@
         <v>1.98392421406192E+33</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -8190,7 +8178,7 @@
         <v>3.2100568094561087E+33</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -8199,7 +8187,7 @@
         <v>5.1939810235180281E+33</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -8208,7 +8196,7 @@
         <v>8.4040378329741368E+33</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -8217,7 +8205,7 @@
         <v>1.3598018856492165E+34</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -8226,7 +8214,7 @@
         <v>2.2002056689466302E+34</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -8235,7 +8223,7 @@
         <v>3.5600075545958467E+34</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -8244,7 +8232,7 @@
         <v>5.7602132235424769E+34</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -8253,7 +8241,7 @@
         <v>9.3202207781383226E+34</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -8262,7 +8250,7 @@
         <v>1.5080434001680799E+35</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -8271,7 +8259,7 @@
         <v>2.4400654779819122E+35</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -8280,7 +8268,7 @@
         <v>3.9481088781499925E+35</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -8289,7 +8277,7 @@
         <v>6.3881743561319051E+35</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -8298,7 +8286,7 @@
         <v>1.0336283234281898E+36</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -8307,7 +8295,7 @@
         <v>1.6724457590413803E+36</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -8316,7 +8304,7 @@
         <v>2.70607408246957E+36</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -8325,7 +8313,7 @@
         <v>4.37851984151095E+36</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -8334,7 +8322,7 @@
         <v>7.0845939239805195E+36</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -8343,7 +8331,7 @@
         <v>1.1463113765491469E+37</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -8352,7 +8340,7 @@
         <v>1.8547707689471989E+37</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -8361,7 +8349,7 @@
         <v>3.0010821454963458E+37</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -8370,7 +8358,7 @@
         <v>4.8558529144435443E+37</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -8379,7 +8367,7 @@
         <v>7.8569350599398901E+37</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -8388,7 +8376,7 @@
         <v>1.2712787974383434E+38</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -8397,7 +8385,7 @@
         <v>2.0569723034323324E+38</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -8406,7 +8394,7 @@
         <v>3.3282511008706759E+38</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -8415,7 +8403,7 @@
         <v>5.3852234043030087E+38</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -8424,7 +8412,7 @@
         <v>8.7134745051736838E+38</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -8433,7 +8421,7 @@
         <v>1.4098697909476691E+39</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -8442,7 +8430,7 @@
         <v>2.2812172414650375E+39</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -8451,7 +8439,7 @@
         <v>3.6910870324127069E+39</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -8460,7 +8448,7 @@
         <v>5.9723042738777447E+39</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -8469,7 +8457,7 @@
         <v>9.6633913062904516E+39</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -8478,7 +8466,7 @@
         <v>1.5635695580168196E+40</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -8487,7 +8475,7 @@
         <v>2.529908688645865E+40</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -8496,7 +8484,7 @@
         <v>4.0934782466626846E+40</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -8505,7 +8493,7 @@
         <v>6.6233869353085492E+40</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -8514,7 +8502,7 @@
         <v>1.0716865181971233E+41</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -8523,7 +8511,7 @@
         <v>1.7340252117279783E+41</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -8532,7 +8520,7 @@
         <v>2.8057117299251016E+41</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -8541,7 +8529,7 @@
         <v>4.5397369416530796E+41</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -8550,7 +8538,7 @@
         <v>7.3454486715781805E+41</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -8559,7 +8547,7 @@
         <v>1.188518561323126E+42</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -8568,7 +8556,7 @@
         <v>1.9230634284809439E+42</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -8577,7 +8565,7 @@
         <v>3.1115819898040701E+42</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -8586,7 +8574,7 @@
         <v>5.034645418285014E+42</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -8595,7 +8583,7 @@
         <v>8.1462274080890834E+42</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -8604,7 +8592,7 @@
         <v>1.3180872826374099E+43</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -8613,7 +8601,7 @@
         <v>2.1327100234463182E+43</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -8622,7 +8610,7 @@
         <v>3.4507973060837281E+43</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
+++ b/2_Course/3_Term/Applied_Math_in_AI/lab_01/ЛР-1_Заварзин_ИИ-б-25-6-о.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\SevSU\2_Course\3_Term\Applied_Math_in_AI\lab_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F573EB-CE40-4ADC-ABBC-7045E042EE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E46BB60-B9C0-422B-B875-8DE32AB08BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="2" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" firstSheet="1" activeTab="2" xr2:uid="{1BBF2652-5E7F-46D7-B5BA-6FA9833463E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Инициализация" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="238">
   <si>
     <t>f(x)</t>
   </si>
@@ -145,21 +145,6 @@
     <t>3 итерация</t>
   </si>
   <si>
-    <t>a =</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b = </t>
-  </si>
-  <si>
-    <t>n =</t>
-  </si>
-  <si>
-    <t>F_{n-1} &gt;=</t>
-  </si>
-  <si>
-    <t>F_13 =</t>
-  </si>
-  <si>
     <t>F_1</t>
   </si>
   <si>
@@ -787,13 +772,31 @@
     <t>F_209</t>
   </si>
   <si>
-    <t xml:space="preserve">f(x_1) = </t>
-  </si>
-  <si>
     <t>F_210</t>
   </si>
   <si>
-    <t>F_14 =</t>
+    <t>Итерация</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>x_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x_2 </t>
+  </si>
+  <si>
+    <t>f(x_1)</t>
+  </si>
+  <si>
+    <t>f(x_2)</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
@@ -846,7 +849,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -865,38 +868,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -941,11 +914,146 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -972,36 +1080,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1019,6 +1097,40 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5686,7 +5798,7 @@
         <f>A18-A2</f>
         <v>16</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="S1" s="16" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5705,7 +5817,7 @@
         <f>(A18+A2)/2</f>
         <v>-2</v>
       </c>
-      <c r="S2" s="26"/>
+      <c r="S2" s="16"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -5722,7 +5834,7 @@
         <f>POWER(L2,4)+8*POWER(L2,3)-6*POWER(L2,2)-72*L2+90</f>
         <v>162</v>
       </c>
-      <c r="S3" s="26"/>
+      <c r="S3" s="16"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -5739,7 +5851,7 @@
         <f>A2+L1/4</f>
         <v>-6</v>
       </c>
-      <c r="S4" s="26"/>
+      <c r="S4" s="16"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -5756,7 +5868,7 @@
         <f>A18-L1/4</f>
         <v>2</v>
       </c>
-      <c r="S5" s="26"/>
+      <c r="S5" s="16"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -5773,7 +5885,7 @@
         <f>POWER(L4,4)+8*POWER(L4,3)-6*POWER(L4,2)-72*L4+90</f>
         <v>-126</v>
       </c>
-      <c r="S6" s="26"/>
+      <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -5790,7 +5902,7 @@
         <f>POWER(L5,4)+8*POWER(L5,3)-6*POWER(L5,2)-72*L5+90</f>
         <v>2</v>
       </c>
-      <c r="S7" s="26"/>
+      <c r="S7" s="16"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
@@ -5800,7 +5912,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="S8" s="26"/>
+      <c r="S8" s="16"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
@@ -5810,16 +5922,16 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="25"/>
-      <c r="S9" s="26"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="15"/>
+      <c r="S9" s="16"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -5829,7 +5941,7 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="S10" s="26"/>
+      <c r="S10" s="16"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
@@ -5846,7 +5958,7 @@
         <f>L2-A2</f>
         <v>8</v>
       </c>
-      <c r="S11" s="26"/>
+      <c r="S11" s="16"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
@@ -5856,16 +5968,16 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="25"/>
-      <c r="S12" s="26"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="15"/>
+      <c r="S12" s="16"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -5875,7 +5987,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="S13" s="26"/>
+      <c r="S13" s="16"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -5885,7 +5997,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="S14" s="26"/>
+      <c r="S14" s="16"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -5895,7 +6007,7 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="S15" s="26"/>
+      <c r="S15" s="16"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -5905,7 +6017,7 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="S16" s="26"/>
+      <c r="S16" s="16"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -5915,7 +6027,7 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="S17" s="26"/>
+      <c r="S17" s="16"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -5925,12 +6037,12 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="S18" s="26"/>
+      <c r="S18" s="16"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="S19" s="26"/>
+      <c r="S19" s="16"/>
     </row>
     <row r="20" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
@@ -5950,7 +6062,7 @@
         <f>A30-A22</f>
         <v>8</v>
       </c>
-      <c r="S21" s="26" t="s">
+      <c r="S21" s="16" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5969,7 +6081,7 @@
         <f>(A30+A22)/2</f>
         <v>-6</v>
       </c>
-      <c r="S22" s="26"/>
+      <c r="S22" s="16"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -5986,7 +6098,7 @@
         <f>POWER(L22,4)+8*POWER(L22,3)-6*POWER(L22,2)-72*L22+90</f>
         <v>-126</v>
       </c>
-      <c r="S23" s="26"/>
+      <c r="S23" s="16"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -6003,7 +6115,7 @@
         <f>A22+L21/4</f>
         <v>-8</v>
       </c>
-      <c r="S24" s="26"/>
+      <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -6020,7 +6132,7 @@
         <f>A30-L21/4</f>
         <v>-4</v>
       </c>
-      <c r="S25" s="26"/>
+      <c r="S25" s="16"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -6037,7 +6149,7 @@
         <f>POWER(L24,4)+8*POWER(L24,3)-6*POWER(L24,2)-72*L24+90</f>
         <v>282</v>
       </c>
-      <c r="S26" s="26"/>
+      <c r="S26" s="16"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -6054,7 +6166,7 @@
         <f>POWER(L25,4)+8*POWER(L25,3)-6*POWER(L25,2)-72*L25+90</f>
         <v>26</v>
       </c>
-      <c r="S27" s="26"/>
+      <c r="S27" s="16"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
@@ -6064,7 +6176,7 @@
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="S28" s="26"/>
+      <c r="S28" s="16"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
@@ -6074,16 +6186,16 @@
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="K29" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="25"/>
-      <c r="S29" s="26"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="15"/>
+      <c r="S29" s="16"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -6093,7 +6205,7 @@
         <f t="shared" si="1"/>
         <v>162</v>
       </c>
-      <c r="S30" s="26"/>
+      <c r="S30" s="16"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K31" s="3" t="s">
@@ -6103,28 +6215,28 @@
         <f>L25-L24</f>
         <v>4</v>
       </c>
-      <c r="S31" s="26"/>
+      <c r="S31" s="16"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K32" s="20" t="s">
+      <c r="K32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="22"/>
-      <c r="S32" s="26"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="12"/>
+      <c r="S32" s="16"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S33" s="26"/>
+      <c r="S33" s="16"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S34" s="26"/>
+      <c r="S34" s="16"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="S35" s="26"/>
+      <c r="S35" s="16"/>
     </row>
     <row r="36" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6141,7 +6253,7 @@
         <f>A42-A38</f>
         <v>4</v>
       </c>
-      <c r="S37" s="27" t="s">
+      <c r="S37" s="17" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6160,7 +6272,7 @@
         <f>(A38+A42)/2</f>
         <v>-6</v>
       </c>
-      <c r="S38" s="27"/>
+      <c r="S38" s="17"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -6177,7 +6289,7 @@
         <f>POWER(L38,4)+8*POWER(L38,3)-6*POWER(L38,2)-72*L38+90</f>
         <v>-126</v>
       </c>
-      <c r="S39" s="27"/>
+      <c r="S39" s="17"/>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -6194,7 +6306,7 @@
         <f>A38+L37/4</f>
         <v>-7</v>
       </c>
-      <c r="S40" s="27"/>
+      <c r="S40" s="17"/>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -6211,7 +6323,7 @@
         <f>A42-L37/4</f>
         <v>-5</v>
       </c>
-      <c r="S41" s="27"/>
+      <c r="S41" s="17"/>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -6228,7 +6340,7 @@
         <f>POWER(L40,4)+8*POWER(L40,3)-6*POWER(L40,2)-72*L40+90</f>
         <v>-43</v>
       </c>
-      <c r="S42" s="27"/>
+      <c r="S42" s="17"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
@@ -6240,31 +6352,31 @@
         <f>POWER(L41,4)+8*POWER(L41,3)-6*POWER(L41,2)-72*L41+90</f>
         <v>-75</v>
       </c>
-      <c r="S43" s="27"/>
+      <c r="S43" s="17"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
-      <c r="S44" s="27"/>
+      <c r="S44" s="17"/>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
-      <c r="K45" s="23" t="s">
+      <c r="K45" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="24"/>
-      <c r="M45" s="24"/>
-      <c r="N45" s="24"/>
-      <c r="O45" s="24"/>
-      <c r="P45" s="24"/>
-      <c r="Q45" s="25"/>
-      <c r="S45" s="27"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+      <c r="Q45" s="15"/>
+      <c r="S45" s="17"/>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
-      <c r="S46" s="27"/>
+      <c r="S46" s="17"/>
     </row>
     <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
@@ -6276,42 +6388,42 @@
         <f>L41-L40</f>
         <v>2</v>
       </c>
-      <c r="S47" s="27"/>
+      <c r="S47" s="17"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="K48" s="20" t="s">
+      <c r="K48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="21"/>
-      <c r="M48" s="21"/>
-      <c r="N48" s="21"/>
-      <c r="O48" s="21"/>
-      <c r="P48" s="21"/>
-      <c r="Q48" s="22"/>
-      <c r="S48" s="27"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="12"/>
+      <c r="S48" s="17"/>
     </row>
     <row r="49" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S49" s="27"/>
+      <c r="S49" s="17"/>
     </row>
     <row r="50" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S50" s="27"/>
+      <c r="S50" s="17"/>
     </row>
     <row r="51" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S51" s="27"/>
+      <c r="S51" s="17"/>
     </row>
     <row r="52" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S52" s="27"/>
+      <c r="S52" s="17"/>
     </row>
     <row r="53" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S53" s="27"/>
+      <c r="S53" s="17"/>
     </row>
     <row r="54" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S54" s="27"/>
+      <c r="S54" s="17"/>
     </row>
     <row r="55" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S55" s="27"/>
+      <c r="S55" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -6332,29 +6444,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81ADA57-1C13-42F7-B065-32BF7F0FC547}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="9"/>
+    <col min="11" max="12" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="11">
-        <f>A2</f>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K1" s="18"/>
+      <c r="L1" s="19"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>-10</v>
       </c>
@@ -6362,15 +6472,33 @@
         <f>POWER(A2,4)+8*POWER(A2,3)-6*POWER(A2,2)-72*A2+90</f>
         <v>2210</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="11">
-        <f>A18</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D2" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>-9</v>
       </c>
@@ -6378,22 +6506,37 @@
         <f t="shared" ref="B3:B18" si="0">POWER(A3,4)+8*POWER(A3,3)-6*POWER(A3,2)-72*A3+90</f>
         <v>981</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="11">
-        <f>E2-E1</f>
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <f>Числа_Фибоначчи!A13</f>
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D3" s="24">
+        <v>1</v>
+      </c>
+      <c r="E3" s="25">
+        <v>14</v>
+      </c>
+      <c r="F3" s="25">
+        <v>-10</v>
+      </c>
+      <c r="G3" s="25">
+        <v>6</v>
+      </c>
+      <c r="H3" s="25">
+        <f>F3+(Числа_Фибоначчи!A15/Числа_Фибоначчи!A17)*(G3-F3)</f>
+        <v>-3.8885410144020041</v>
+      </c>
+      <c r="I3" s="25">
+        <f>F3+(Числа_Фибоначчи!A16/Числа_Фибоначчи!A17)*(G3-F3)</f>
+        <v>-0.11145898559799683</v>
+      </c>
+      <c r="J3" s="25">
+        <f>POWER(H3,4)+8*POWER(H3,3)-6*POWER(H3,2)-72*H3+90</f>
+        <v>37.506272869048132</v>
+      </c>
+      <c r="K3" s="26">
+        <f>POWER(I3,4)+8*POWER(I3,3)-6*POWER(I3,2)-72*I3+90</f>
+        <v>97.939585329912319</v>
+      </c>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>-8</v>
       </c>
@@ -6401,22 +6544,38 @@
         <f t="shared" si="0"/>
         <v>282</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="11">
-        <f>E3/0.05</f>
-        <v>320</v>
-      </c>
-      <c r="G4" t="s">
-        <v>236</v>
-      </c>
-      <c r="H4">
-        <f>Числа_Фибоначчи!A14</f>
-        <v>377</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D4" s="24">
+        <v>2</v>
+      </c>
+      <c r="E4" s="25">
+        <v>13</v>
+      </c>
+      <c r="F4" s="25">
+        <v>-10</v>
+      </c>
+      <c r="G4" s="25">
+        <f>I3</f>
+        <v>-0.11145898559799683</v>
+      </c>
+      <c r="H4" s="25">
+        <f>F4+(Числа_Фибоначчи!A16/Числа_Фибоначчи!A18)*(G4-F4)</f>
+        <v>-6.2229140939571295</v>
+      </c>
+      <c r="I4" s="25">
+        <f>H3</f>
+        <v>-3.8885410144020041</v>
+      </c>
+      <c r="J4" s="25">
+        <f t="shared" ref="J4:J6" si="1">POWER(H4,4)+8*POWER(H4,3)-6*POWER(H4,2)-72*H4+90</f>
+        <v>-122.5407169842623</v>
+      </c>
+      <c r="K4" s="26">
+        <f t="shared" ref="K4:K6" si="2">POWER(I4,4)+8*POWER(I4,3)-6*POWER(I4,2)-72*I4+90</f>
+        <v>37.506272869048132</v>
+      </c>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>-7</v>
       </c>
@@ -6424,14 +6583,38 @@
         <f t="shared" si="0"/>
         <v>-43</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D5" s="24">
+        <v>3</v>
+      </c>
+      <c r="E5" s="25">
+        <v>12</v>
+      </c>
+      <c r="F5" s="25">
+        <v>-10</v>
+      </c>
+      <c r="G5" s="25">
+        <f>I4</f>
+        <v>-3.8885410144020041</v>
+      </c>
+      <c r="H5" s="25">
+        <f>F5+(Числа_Фибоначчи!A17/Числа_Фибоначчи!A19)*(G5-F5)</f>
+        <v>-7.6656302320019138</v>
+      </c>
+      <c r="I5" s="25">
+        <f>F5+(Числа_Фибоначчи!A18/Числа_Фибоначчи!A19)*(G5-F5)</f>
+        <v>-6.2229107824000902</v>
+      </c>
+      <c r="J5" s="25">
+        <f t="shared" si="1"/>
+        <v>138.73823135149269</v>
+      </c>
+      <c r="K5" s="26">
+        <f t="shared" si="2"/>
+        <v>-122.54082247015526</v>
+      </c>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>-6</v>
       </c>
@@ -6439,15 +6622,39 @@
         <f t="shared" si="0"/>
         <v>-126</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="13">
-        <f>E1+(Числа_Фибоначчи!A15/Числа_Фибоначчи!A17)*E3</f>
+      <c r="D6" s="27">
+        <v>4</v>
+      </c>
+      <c r="E6" s="28">
+        <v>11</v>
+      </c>
+      <c r="F6" s="28">
+        <f>H5</f>
+        <v>-7.6656302320019138</v>
+      </c>
+      <c r="G6" s="28">
+        <f>G5</f>
         <v>-3.8885410144020041</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H6" s="28">
+        <f>F6+(Числа_Фибоначчи!A18/Числа_Фибоначчи!A20)*(G6-F6)</f>
+        <v>-6.2229105663288662</v>
+      </c>
+      <c r="I6" s="28">
+        <f>F6+(Числа_Фибоначчи!A19/Числа_Фибоначчи!A20)*(G6-F6)</f>
+        <v>-5.3312606800750517</v>
+      </c>
+      <c r="J6" s="28">
+        <f t="shared" si="1"/>
+        <v>-122.54082935280059</v>
+      </c>
+      <c r="K6" s="29">
+        <f t="shared" si="2"/>
+        <v>-101.06908578406603</v>
+      </c>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>-5</v>
       </c>
@@ -6455,15 +6662,10 @@
         <f t="shared" si="0"/>
         <v>-75</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="13">
-        <f>E1+(Числа_Фибоначчи!A16/Числа_Фибоначчи!A17)*E3</f>
-        <v>-0.11145898559799683</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K7" s="18"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>-4</v>
       </c>
@@ -6471,15 +6673,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="13">
-        <f>POWER(E6,4)+8*POWER(E6,3)-6*POWER(E6,2)-72*E6+90</f>
-        <v>37.506272869048132</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>-3</v>
       </c>
@@ -6487,15 +6684,10 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="13">
-        <f>POWER(E7,4)+8*POWER(E7,3)-6*POWER(E7,2)-72*E7+90</f>
-        <v>97.939585329912319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K9" s="18"/>
+      <c r="L9" s="19"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>-2</v>
       </c>
@@ -6503,15 +6695,10 @@
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="13">
-        <f>E7</f>
-        <v>-0.11145898559799683</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>-1</v>
       </c>
@@ -6519,15 +6706,10 @@
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="13">
-        <f>E6</f>
-        <v>-3.8885410144020041</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0</v>
       </c>
@@ -6535,15 +6717,10 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="15">
-        <f>E5-1</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K12" s="18"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1</v>
       </c>
@@ -6551,15 +6728,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="15">
-        <f>E1+(Числа_Фибоначчи!A14/Числа_Фибоначчи!A16)*(E10-E1)</f>
-        <v>-6.2229179711959928</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K13" s="18"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -6567,15 +6739,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="15">
-        <f>POWER(E13,4)+8*POWER(E13,3)-6*POWER(E13,2)-72*E13+90</f>
-        <v>-122.54059347706982</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K14" s="18"/>
+      <c r="L14" s="19"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>3</v>
       </c>
@@ -6583,15 +6750,10 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="15">
-        <f>E11</f>
-        <v>-3.8885410144020041</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -6599,15 +6761,10 @@
         <f t="shared" si="0"/>
         <v>474</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="15">
-        <f>E13</f>
-        <v>-6.2229179711959928</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K16" s="18"/>
+      <c r="L16" s="19"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>5</v>
       </c>
@@ -6615,15 +6772,10 @@
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="17">
-        <f>E12-1</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="K17" s="18"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>6</v>
       </c>
@@ -6631,85 +6783,40 @@
         <f t="shared" si="0"/>
         <v>2466</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="17">
-        <f>E1+(Числа_Фибоначчи!A13/Числа_Фибоначчи!A15)*(E15-E1)</f>
-        <v>-7.6656230432060113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="E19" s="17">
-        <f>POWER(E18,4)+8*POWER(E18,3)-6*POWER(E18,2)-72*E18+90</f>
-        <v>138.73556061626778</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D20" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="17">
-        <f>E18</f>
-        <v>-7.6656230432060113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D21" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="17">
-        <f>E16</f>
-        <v>-6.2229179711959928</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D22" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="19">
-        <f>E17-1</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D23" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="19">
-        <f>E20+(Числа_Фибоначчи!A12/Числа_Фибоначчи!A13)*(E15-E20)</f>
-        <v>-5.33128908549023</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="19">
-        <f>POWER(E23,4)+8*POWER(E23,3)-6*POWER(E23,2)-72*E23+90</f>
-        <v>-101.07101742715895</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="19">
-        <f>E21</f>
-        <v>-6.2229179711959928</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D26" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="19">
-        <f>E23</f>
-        <v>-5.33128908549023</v>
-      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K19" s="18"/>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K20" s="18"/>
+      <c r="L20" s="19"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K21" s="18"/>
+      <c r="L21" s="19"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K22" s="18"/>
+      <c r="L22" s="19"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K23" s="18"/>
+      <c r="L23" s="19"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K24" s="18"/>
+      <c r="L24" s="19"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K25" s="18"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" s="18"/>
+      <c r="L26" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6730,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -6738,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -6747,7 +6854,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -6756,7 +6863,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -6765,7 +6872,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -6774,7 +6881,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -6783,7 +6890,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -6792,7 +6899,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -6801,7 +6908,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6810,7 +6917,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -6819,7 +6926,7 @@
         <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -6828,7 +6935,7 @@
         <v>144</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6837,7 +6944,7 @@
         <v>233</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -6846,7 +6953,7 @@
         <v>377</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6855,7 +6962,7 @@
         <v>610</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -6864,7 +6971,7 @@
         <v>987</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -6873,7 +6980,7 @@
         <v>1597</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6882,7 +6989,7 @@
         <v>2584</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -6891,7 +6998,7 @@
         <v>4181</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -6900,7 +7007,7 @@
         <v>6765</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -6909,7 +7016,7 @@
         <v>10946</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -6918,7 +7025,7 @@
         <v>17711</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -6927,7 +7034,7 @@
         <v>28657</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -6936,7 +7043,7 @@
         <v>46368</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -6945,7 +7052,7 @@
         <v>75025</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -6954,7 +7061,7 @@
         <v>121393</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -6963,7 +7070,7 @@
         <v>196418</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -6972,7 +7079,7 @@
         <v>317811</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -6981,7 +7088,7 @@
         <v>514229</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -6990,7 +7097,7 @@
         <v>832040</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -6999,7 +7106,7 @@
         <v>1346269</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -7008,7 +7115,7 @@
         <v>2178309</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -7017,7 +7124,7 @@
         <v>3524578</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -7026,7 +7133,7 @@
         <v>5702887</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -7035,7 +7142,7 @@
         <v>9227465</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -7044,7 +7151,7 @@
         <v>14930352</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -7053,7 +7160,7 @@
         <v>24157817</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -7062,7 +7169,7 @@
         <v>39088169</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -7071,7 +7178,7 @@
         <v>63245986</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -7080,7 +7187,7 @@
         <v>102334155</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -7089,7 +7196,7 @@
         <v>165580141</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -7098,7 +7205,7 @@
         <v>267914296</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -7107,7 +7214,7 @@
         <v>433494437</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -7116,7 +7223,7 @@
         <v>701408733</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -7125,7 +7232,7 @@
         <v>1134903170</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -7134,7 +7241,7 @@
         <v>1836311903</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -7143,7 +7250,7 @@
         <v>2971215073</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -7152,7 +7259,7 @@
         <v>4807526976</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -7161,7 +7268,7 @@
         <v>7778742049</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -7170,7 +7277,7 @@
         <v>12586269025</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -7179,7 +7286,7 @@
         <v>20365011074</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -7188,7 +7295,7 @@
         <v>32951280099</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -7197,7 +7304,7 @@
         <v>53316291173</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -7206,7 +7313,7 @@
         <v>86267571272</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -7215,7 +7322,7 @@
         <v>139583862445</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -7224,7 +7331,7 @@
         <v>225851433717</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -7233,7 +7340,7 @@
         <v>365435296162</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -7242,7 +7349,7 @@
         <v>591286729879</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -7251,7 +7358,7 @@
         <v>956722026041</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -7260,7 +7367,7 @@
         <v>1548008755920</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -7269,7 +7376,7 @@
         <v>2504730781961</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -7278,7 +7385,7 @@
         <v>4052739537881</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -7287,7 +7394,7 @@
         <v>6557470319842</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -7296,7 +7403,7 @@
         <v>10610209857723</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -7305,7 +7412,7 @@
         <v>17167680177565</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -7314,7 +7421,7 @@
         <v>27777890035288</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -7323,7 +7430,7 @@
         <v>44945570212853</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -7332,7 +7439,7 @@
         <v>72723460248141</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -7341,7 +7448,7 @@
         <v>117669030460994</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -7350,7 +7457,7 @@
         <v>190392490709135</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -7359,7 +7466,7 @@
         <v>308061521170129</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -7368,7 +7475,7 @@
         <v>498454011879264</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -7377,7 +7484,7 @@
         <v>806515533049393</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -7386,7 +7493,7 @@
         <v>1304969544928657</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -7395,7 +7502,7 @@
         <v>2111485077978050</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -7404,7 +7511,7 @@
         <v>3416454622906707</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -7413,7 +7520,7 @@
         <v>5527939700884757</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -7422,7 +7529,7 @@
         <v>8944394323791464</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -7431,7 +7538,7 @@
         <v>1.447233402467622E+16</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -7440,7 +7547,7 @@
         <v>2.3416728348467684E+16</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -7449,7 +7556,7 @@
         <v>3.7889062373143904E+16</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -7458,7 +7565,7 @@
         <v>6.1305790721611584E+16</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -7467,7 +7574,7 @@
         <v>9.9194853094755488E+16</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -7476,7 +7583,7 @@
         <v>1.6050064381636707E+17</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -7485,7 +7592,7 @@
         <v>2.5969549691112256E+17</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -7494,7 +7601,7 @@
         <v>4.2019614072748966E+17</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -7503,7 +7610,7 @@
         <v>6.7989163763861222E+17</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -7512,7 +7619,7 @@
         <v>1.1000877783661019E+18</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -7521,7 +7628,7 @@
         <v>1.779979416004714E+18</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -7530,7 +7637,7 @@
         <v>2.880067194370816E+18</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -7539,7 +7646,7 @@
         <v>4.6600466103755305E+18</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -7548,7 +7655,7 @@
         <v>7.5401138047463465E+18</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -7557,7 +7664,7 @@
         <v>1.2200160415121877E+19</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -7566,7 +7673,7 @@
         <v>1.9740274219868226E+19</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -7575,7 +7682,7 @@
         <v>3.19404346349901E+19</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -7584,7 +7691,7 @@
         <v>5.1680708854858326E+19</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -7593,7 +7700,7 @@
         <v>8.3621143489848426E+19</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,7 +7709,7 @@
         <v>1.3530185234470676E+20</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -7611,7 +7718,7 @@
         <v>2.189229958345552E+20</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -7620,7 +7727,7 @@
         <v>3.54224848179262E+20</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -7629,7 +7736,7 @@
         <v>5.731478440138172E+20</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7745,7 @@
         <v>9.273726921930792E+20</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -7647,7 +7754,7 @@
         <v>1.5005205362068963E+21</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -7656,7 +7763,7 @@
         <v>2.4278932283999755E+21</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -7665,7 +7772,7 @@
         <v>3.9284137646068717E+21</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -7674,7 +7781,7 @@
         <v>6.3563069930068477E+21</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -7683,7 +7790,7 @@
         <v>1.028472075761372E+22</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -7692,7 +7799,7 @@
         <v>1.6641027750620568E+22</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -7701,7 +7808,7 @@
         <v>2.6925748508234288E+22</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -7710,7 +7817,7 @@
         <v>4.3566776258854857E+22</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -7719,7 +7826,7 @@
         <v>7.0492524767089141E+22</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -7728,7 +7835,7 @@
         <v>1.1405930102594401E+23</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -7737,7 +7844,7 @@
         <v>1.8455182579303315E+23</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -7746,7 +7853,7 @@
         <v>2.9861112681897715E+23</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -7755,7 +7862,7 @@
         <v>4.831629526120103E+23</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -7764,7 +7871,7 @@
         <v>7.8177407943098749E+23</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -7773,7 +7880,7 @@
         <v>1.2649370320429978E+24</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -7782,7 +7889,7 @@
         <v>2.0467111114739851E+24</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -7791,7 +7898,7 @@
         <v>3.3116481435169827E+24</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -7800,7 +7907,7 @@
         <v>5.3583592549909684E+24</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -7809,7 +7916,7 @@
         <v>8.670007398507951E+24</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -7818,7 +7925,7 @@
         <v>1.4028366653498919E+25</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -7827,7 +7934,7 @@
         <v>2.2698374052006868E+25</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -7836,7 +7943,7 @@
         <v>3.6726740705505786E+25</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -7845,7 +7952,7 @@
         <v>5.9425114757512654E+25</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -7854,7 +7961,7 @@
         <v>9.6151855463018439E+25</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -7863,7 +7970,7 @@
         <v>1.5557697022053108E+26</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -7872,7 +7979,7 @@
         <v>2.5172882568354952E+26</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -7881,7 +7988,7 @@
         <v>4.0730579590408064E+26</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -7890,7 +7997,7 @@
         <v>6.590346215876301E+26</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -7899,7 +8006,7 @@
         <v>1.0663404174917107E+27</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -7908,7 +8015,7 @@
         <v>1.7253750390793408E+27</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -7917,7 +8024,7 @@
         <v>2.7917154565710519E+27</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -7926,7 +8033,7 @@
         <v>4.5170904956503927E+27</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -7935,7 +8042,7 @@
         <v>7.3088059522214451E+27</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -7944,7 +8051,7 @@
         <v>1.1825896447871837E+28</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -7953,7 +8060,7 @@
         <v>1.9134702400093282E+28</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -7962,7 +8069,7 @@
         <v>3.0960598847965122E+28</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -7971,7 +8078,7 @@
         <v>5.0095301248058406E+28</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -7980,7 +8087,7 @@
         <v>8.1055900096023528E+28</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -7989,7 +8096,7 @@
         <v>1.3115120134408193E+29</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -7998,7 +8105,7 @@
         <v>2.1220710144010545E+29</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -8007,7 +8114,7 @@
         <v>3.4335830278418734E+29</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -8016,7 +8123,7 @@
         <v>5.5556540422429276E+29</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -8025,7 +8132,7 @@
         <v>8.9892370700848011E+29</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -8034,7 +8141,7 @@
         <v>1.454489111232773E+30</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -8043,7 +8150,7 @@
         <v>2.3534128182412531E+30</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -8052,7 +8159,7 @@
         <v>3.8079019294740258E+30</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -8061,7 +8168,7 @@
         <v>6.1613147477152787E+30</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -8070,7 +8177,7 @@
         <v>9.9692166771893045E+30</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -8079,7 +8186,7 @@
         <v>1.6130531424904583E+31</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -8088,7 +8195,7 @@
         <v>2.6099748102093888E+31</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -8097,7 +8204,7 @@
         <v>4.2230279526998473E+31</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -8106,7 +8213,7 @@
         <v>6.8330027629092365E+31</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -8115,7 +8222,7 @@
         <v>1.1056030715609085E+32</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -8124,7 +8231,7 @@
         <v>1.7889033478518321E+32</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -8133,7 +8240,7 @@
         <v>2.8945064194127406E+32</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -8142,7 +8249,7 @@
         <v>4.6834097672645727E+32</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -8151,7 +8258,7 @@
         <v>7.5779161866773133E+32</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -8160,7 +8267,7 @@
         <v>1.2261325953941887E+33</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -8169,7 +8276,7 @@
         <v>1.98392421406192E+33</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -8178,7 +8285,7 @@
         <v>3.2100568094561087E+33</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -8187,7 +8294,7 @@
         <v>5.1939810235180281E+33</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -8196,7 +8303,7 @@
         <v>8.4040378329741368E+33</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -8205,7 +8312,7 @@
         <v>1.3598018856492165E+34</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -8214,7 +8321,7 @@
         <v>2.2002056689466302E+34</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -8223,7 +8330,7 @@
         <v>3.5600075545958467E+34</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -8232,7 +8339,7 @@
         <v>5.7602132235424769E+34</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -8241,7 +8348,7 @@
         <v>9.3202207781383226E+34</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -8250,7 +8357,7 @@
         <v>1.5080434001680799E+35</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -8259,7 +8366,7 @@
         <v>2.4400654779819122E+35</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -8268,7 +8375,7 @@
         <v>3.9481088781499925E+35</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -8277,7 +8384,7 @@
         <v>6.3881743561319051E+35</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -8286,7 +8393,7 @@
         <v>1.0336283234281898E+36</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -8295,7 +8402,7 @@
         <v>1.6724457590413803E+36</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -8304,7 +8411,7 @@
         <v>2.70607408246957E+36</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -8313,7 +8420,7 @@
         <v>4.37851984151095E+36</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -8322,7 +8429,7 @@
         <v>7.0845939239805195E+36</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -8331,7 +8438,7 @@
         <v>1.1463113765491469E+37</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -8340,7 +8447,7 @@
         <v>1.8547707689471989E+37</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -8349,7 +8456,7 @@
         <v>3.0010821454963458E+37</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -8358,7 +8465,7 @@
         <v>4.8558529144435443E+37</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -8367,7 +8474,7 @@
         <v>7.8569350599398901E+37</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -8376,7 +8483,7 @@
         <v>1.2712787974383434E+38</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -8385,7 +8492,7 @@
         <v>2.0569723034323324E+38</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -8394,7 +8501,7 @@
         <v>3.3282511008706759E+38</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -8403,7 +8510,7 @@
         <v>5.3852234043030087E+38</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -8412,7 +8519,7 @@
         <v>8.7134745051736838E+38</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -8421,7 +8528,7 @@
         <v>1.4098697909476691E+39</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -8430,7 +8537,7 @@
         <v>2.2812172414650375E+39</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -8439,7 +8546,7 @@
         <v>3.6910870324127069E+39</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -8448,7 +8555,7 @@
         <v>5.9723042738777447E+39</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -8457,7 +8564,7 @@
         <v>9.6633913062904516E+39</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -8466,7 +8573,7 @@
         <v>1.5635695580168196E+40</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -8475,7 +8582,7 @@
         <v>2.529908688645865E+40</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -8484,7 +8591,7 @@
         <v>4.0934782466626846E+40</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -8493,7 +8600,7 @@
         <v>6.6233869353085492E+40</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -8502,7 +8609,7 @@
         <v>1.0716865181971233E+41</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -8511,7 +8618,7 @@
         <v>1.7340252117279783E+41</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -8520,7 +8627,7 @@
         <v>2.8057117299251016E+41</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -8529,7 +8636,7 @@
         <v>4.5397369416530796E+41</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -8538,7 +8645,7 @@
         <v>7.3454486715781805E+41</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -8547,7 +8654,7 @@
         <v>1.188518561323126E+42</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -8556,7 +8663,7 @@
         <v>1.9230634284809439E+42</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -8565,7 +8672,7 @@
         <v>3.1115819898040701E+42</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -8574,7 +8681,7 @@
         <v>5.034645418285014E+42</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -8583,7 +8690,7 @@
         <v>8.1462274080890834E+42</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -8592,7 +8699,7 @@
         <v>1.3180872826374099E+43</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -8601,7 +8708,7 @@
         <v>2.1327100234463182E+43</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -8610,7 +8717,7 @@
         <v>3.4507973060837281E+43</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
